--- a/inputs/data_symbols_TD/11_LTAN06_800km_1213COLD_MY_ALL_HEAT_MY_Black.xlsx
+++ b/inputs/data_symbols_TD/11_LTAN06_800km_1213COLD_MY_ALL_HEAT_MY_Black.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\inputs\data_symbols_TD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4FE62117-5EFD-4FE1-AE0E-18E414A457D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{ED96E69D-DCA6-404F-9952-9A7FB06EECD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="18900" windowHeight="10965" xr2:uid="{DAA09026-065C-4463-A2C1-ED3B50DFC856}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="18900" windowHeight="10965" xr2:uid="{AD03C37C-919F-4AF3-BE2B-FE497CDDD6D2}"/>
   </bookViews>
   <sheets>
     <sheet name="11_LTAN06_800km_1213COLD_MY_ALL" sheetId="1" r:id="rId1"/>
@@ -1002,7 +1002,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5ACBB3E2-AE98-4A79-ACB0-4D55892333C4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E57D1B09-8D91-48D4-830C-FDFF200658F4}">
   <dimension ref="A1:D303"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1031,7 +1031,7 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>99.116680000000002</v>
+        <v>99.056380000000004</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
@@ -1045,7 +1045,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>99.116680000000002</v>
+        <v>99.056380000000004</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.4">
@@ -1059,7 +1059,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>99.116990000000001</v>
+        <v>99.05668</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.4">
@@ -1073,7 +1073,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>99.118110000000001</v>
+        <v>99.057779999999994</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.4">
@@ -1087,7 +1087,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>99.120360000000005</v>
+        <v>99.059979999999996</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
@@ -1101,7 +1101,7 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>99.123940000000005</v>
+        <v>99.063500000000005</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">
@@ -1115,7 +1115,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>99.129040000000003</v>
+        <v>99.068510000000003</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>99.135819999999995</v>
+        <v>99.075180000000003</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.4">
@@ -1143,7 +1143,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>99.144419999999997</v>
+        <v>99.083650000000006</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.4">
@@ -1157,7 +1157,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>99.154960000000003</v>
+        <v>99.094059999999999</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.4">
@@ -1171,7 +1171,7 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>99.167559999999995</v>
+        <v>99.106520000000003</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.4">
@@ -1185,7 +1185,7 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>99.182310000000001</v>
+        <v>99.121120000000005</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.4">
@@ -1199,7 +1199,7 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>99.199269999999999</v>
+        <v>99.137919999999994</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.4">
@@ -1213,7 +1213,7 @@
         <v>0</v>
       </c>
       <c r="D15">
-        <v>99.218500000000006</v>
+        <v>99.156959999999998</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.4">
@@ -1227,7 +1227,7 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>99.24</v>
+        <v>99.178280000000001</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.4">
@@ -1241,7 +1241,7 @@
         <v>0</v>
       </c>
       <c r="D17">
-        <v>99.26379</v>
+        <v>99.20187</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.4">
@@ -1255,7 +1255,7 @@
         <v>0</v>
       </c>
       <c r="D18">
-        <v>99.289839999999998</v>
+        <v>99.227710000000002</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.4">
@@ -1269,7 +1269,7 @@
         <v>0</v>
       </c>
       <c r="D19">
-        <v>99.318119999999993</v>
+        <v>99.255780000000001</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.4">
@@ -1283,7 +1283,7 @@
         <v>0</v>
       </c>
       <c r="D20">
-        <v>99.348569999999995</v>
+        <v>99.286019999999994</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.4">
@@ -1297,7 +1297,7 @@
         <v>3</v>
       </c>
       <c r="D21">
-        <v>99.377290000000002</v>
+        <v>99.314570000000003</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.4">
@@ -1311,7 +1311,7 @@
         <v>3</v>
       </c>
       <c r="D22">
-        <v>99.399739999999994</v>
+        <v>99.336969999999994</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.4">
@@ -1325,7 +1325,7 @@
         <v>3</v>
       </c>
       <c r="D23">
-        <v>99.415000000000006</v>
+        <v>99.352310000000003</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.4">
@@ -1339,7 +1339,7 @@
         <v>3</v>
       </c>
       <c r="D24">
-        <v>99.422330000000002</v>
+        <v>99.359859999999998</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.4">
@@ -1353,7 +1353,7 @@
         <v>3</v>
       </c>
       <c r="D25">
-        <v>99.421090000000007</v>
+        <v>99.358949999999993</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.4">
@@ -1367,7 +1367,7 @@
         <v>3</v>
       </c>
       <c r="D26">
-        <v>99.410640000000001</v>
+        <v>99.348920000000007</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.4">
@@ -1381,7 +1381,7 @@
         <v>3</v>
       </c>
       <c r="D27">
-        <v>99.390370000000004</v>
+        <v>99.329149999999998</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.4">
@@ -1395,7 +1395,7 @@
         <v>3</v>
       </c>
       <c r="D28">
-        <v>99.359740000000002</v>
+        <v>99.299090000000007</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.4">
@@ -1409,7 +1409,7 @@
         <v>3</v>
       </c>
       <c r="D29">
-        <v>99.318280000000001</v>
+        <v>99.258279999999999</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.4">
@@ -1423,7 +1423,7 @@
         <v>3</v>
       </c>
       <c r="D30">
-        <v>99.265680000000003</v>
+        <v>99.206370000000007</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.4">
@@ -1437,7 +1437,7 @@
         <v>3</v>
       </c>
       <c r="D31">
-        <v>99.201679999999996</v>
+        <v>99.143109999999993</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.4">
@@ -1451,7 +1451,7 @@
         <v>3</v>
       </c>
       <c r="D32">
-        <v>99.126199999999997</v>
+        <v>99.068389999999994</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.4">
@@ -1465,7 +1465,7 @@
         <v>3</v>
       </c>
       <c r="D33">
-        <v>99.039230000000003</v>
+        <v>98.982219999999998</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.4">
@@ -1479,7 +1479,7 @@
         <v>3</v>
       </c>
       <c r="D34">
-        <v>98.940889999999996</v>
+        <v>98.884699999999995</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.4">
@@ -1493,7 +1493,7 @@
         <v>3</v>
       </c>
       <c r="D35">
-        <v>98.831379999999996</v>
+        <v>98.776039999999995</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.4">
@@ -1507,7 +1507,7 @@
         <v>3</v>
       </c>
       <c r="D36">
-        <v>98.710980000000006</v>
+        <v>98.656490000000005</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.4">
@@ -1521,7 +1521,7 @@
         <v>3</v>
       </c>
       <c r="D37">
-        <v>98.580029999999994</v>
+        <v>98.526399999999995</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.4">
@@ -1535,7 +1535,7 @@
         <v>0</v>
       </c>
       <c r="D38">
-        <v>98.442070000000001</v>
+        <v>98.389269999999996</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.4">
@@ -1549,7 +1549,7 @@
         <v>0</v>
       </c>
       <c r="D39">
-        <v>98.301240000000007</v>
+        <v>98.249170000000007</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.4">
@@ -1563,7 +1563,7 @@
         <v>0</v>
       </c>
       <c r="D40">
-        <v>98.158910000000006</v>
+        <v>98.107460000000003</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.4">
@@ -1577,7 +1577,7 @@
         <v>0</v>
       </c>
       <c r="D41">
-        <v>98.016350000000003</v>
+        <v>97.965389999999999</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.4">
@@ -1591,7 +1591,7 @@
         <v>0</v>
       </c>
       <c r="D42">
-        <v>97.874780000000001</v>
+        <v>97.824200000000005</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.4">
@@ -1605,7 +1605,7 @@
         <v>0</v>
       </c>
       <c r="D43">
-        <v>97.735380000000006</v>
+        <v>97.685090000000002</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.4">
@@ -1619,7 +1619,7 @@
         <v>0</v>
       </c>
       <c r="D44">
-        <v>97.599310000000003</v>
+        <v>97.549220000000005</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.4">
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>97.467640000000003</v>
+        <v>97.417670000000001</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.4">
@@ -1647,7 +1647,7 @@
         <v>0</v>
       </c>
       <c r="D46">
-        <v>97.341340000000002</v>
+        <v>97.291420000000002</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.4">
@@ -1661,7 +1661,7 @@
         <v>0</v>
       </c>
       <c r="D47">
-        <v>97.221249999999998</v>
+        <v>97.171300000000002</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.4">
@@ -1675,7 +1675,7 @@
         <v>0</v>
       </c>
       <c r="D48">
-        <v>97.108029999999999</v>
+        <v>97.058000000000007</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.4">
@@ -1689,7 +1689,7 @@
         <v>0</v>
       </c>
       <c r="D49">
-        <v>97.002229999999997</v>
+        <v>96.952060000000003</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.4">
@@ -1703,7 +1703,7 @@
         <v>0</v>
       </c>
       <c r="D50">
-        <v>96.904219999999995</v>
+        <v>96.853870000000001</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.4">
@@ -1717,7 +1717,7 @@
         <v>0</v>
       </c>
       <c r="D51">
-        <v>96.814279999999997</v>
+        <v>96.7637</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.4">
@@ -1731,7 +1731,7 @@
         <v>0</v>
       </c>
       <c r="D52">
-        <v>96.732529999999997</v>
+        <v>96.681709999999995</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.4">
@@ -1745,7 +1745,7 @@
         <v>0</v>
       </c>
       <c r="D53">
-        <v>96.659019999999998</v>
+        <v>96.607919999999993</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.4">
@@ -1759,7 +1759,7 @@
         <v>0</v>
       </c>
       <c r="D54">
-        <v>96.593699999999998</v>
+        <v>96.542310000000001</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.4">
@@ -1773,7 +1773,7 @@
         <v>0</v>
       </c>
       <c r="D55">
-        <v>96.536450000000002</v>
+        <v>96.484769999999997</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.4">
@@ -1787,7 +1787,7 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>96.487120000000004</v>
+        <v>96.435109999999995</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.4">
@@ -1801,7 +1801,7 @@
         <v>0</v>
       </c>
       <c r="D57">
-        <v>96.445490000000007</v>
+        <v>96.393140000000002</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.4">
@@ -1815,7 +1815,7 @@
         <v>0</v>
       </c>
       <c r="D58">
-        <v>96.411339999999996</v>
+        <v>96.358630000000005</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.4">
@@ -1829,7 +1829,7 @@
         <v>0</v>
       </c>
       <c r="D59">
-        <v>96.384399999999999</v>
+        <v>96.331310000000002</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.4">
@@ -1843,7 +1843,7 @@
         <v>0</v>
       </c>
       <c r="D60">
-        <v>96.364379999999997</v>
+        <v>96.310910000000007</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.4">
@@ -1857,7 +1857,7 @@
         <v>0</v>
       </c>
       <c r="D61">
-        <v>96.350999999999999</v>
+        <v>96.297139999999999</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.4">
@@ -1871,7 +1871,7 @@
         <v>0</v>
       </c>
       <c r="D62">
-        <v>96.34393</v>
+        <v>96.289689999999993</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.4">
@@ -1885,7 +1885,7 @@
         <v>0</v>
       </c>
       <c r="D63">
-        <v>96.342860000000002</v>
+        <v>96.288250000000005</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.4">
@@ -1899,7 +1899,7 @@
         <v>0</v>
       </c>
       <c r="D64">
-        <v>96.347470000000001</v>
+        <v>96.292479999999998</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.4">
@@ -1913,7 +1913,7 @@
         <v>0</v>
       </c>
       <c r="D65">
-        <v>96.357429999999994</v>
+        <v>96.302070000000001</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.4">
@@ -1927,7 +1927,7 @@
         <v>0</v>
       </c>
       <c r="D66">
-        <v>96.372410000000002</v>
+        <v>96.316689999999994</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.4">
@@ -1941,7 +1941,7 @@
         <v>0</v>
       </c>
       <c r="D67">
-        <v>96.392099999999999</v>
+        <v>96.336020000000005</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.4">
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>96.416169999999994</v>
+        <v>96.359740000000002</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.4">
@@ -1969,7 +1969,7 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>96.444310000000002</v>
+        <v>96.387550000000005</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.4">
@@ -1983,7 +1983,7 @@
         <v>0</v>
       </c>
       <c r="D70">
-        <v>96.476200000000006</v>
+        <v>96.419150000000002</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.4">
@@ -1997,7 +1997,7 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>96.51155</v>
+        <v>96.454229999999995</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.4">
@@ -2011,7 +2011,7 @@
         <v>0</v>
       </c>
       <c r="D72">
-        <v>96.5501</v>
+        <v>96.492509999999996</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.4">
@@ -2025,7 +2025,7 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>96.591560000000001</v>
+        <v>96.533709999999999</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.4">
@@ -2039,7 +2039,7 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>96.635670000000005</v>
+        <v>96.577569999999994</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.4">
@@ -2053,7 +2053,7 @@
         <v>0</v>
       </c>
       <c r="D75">
-        <v>96.682190000000006</v>
+        <v>96.623810000000006</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.4">
@@ -2067,7 +2067,7 @@
         <v>0</v>
       </c>
       <c r="D76">
-        <v>96.730850000000004</v>
+        <v>96.672200000000004</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.4">
@@ -2081,7 +2081,7 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>96.781419999999997</v>
+        <v>96.72251</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.4">
@@ -2095,7 +2095,7 @@
         <v>0</v>
       </c>
       <c r="D78">
-        <v>96.833669999999998</v>
+        <v>96.774510000000006</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.4">
@@ -2109,7 +2109,7 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>96.887389999999996</v>
+        <v>96.828019999999995</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.4">
@@ -2123,7 +2123,7 @@
         <v>0</v>
       </c>
       <c r="D80">
-        <v>96.942400000000006</v>
+        <v>96.882819999999995</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.4">
@@ -2137,7 +2137,7 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>96.998519999999999</v>
+        <v>96.938739999999996</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.4">
@@ -2151,7 +2151,7 @@
         <v>0</v>
       </c>
       <c r="D82">
-        <v>97.055580000000006</v>
+        <v>96.995590000000007</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.4">
@@ -2165,7 +2165,7 @@
         <v>0</v>
       </c>
       <c r="D83">
-        <v>97.113420000000005</v>
+        <v>97.053229999999999</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.4">
@@ -2179,7 +2179,7 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>97.171890000000005</v>
+        <v>97.111500000000007</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.4">
@@ -2193,7 +2193,7 @@
         <v>0</v>
       </c>
       <c r="D85">
-        <v>97.230879999999999</v>
+        <v>97.170280000000005</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.4">
@@ -2207,7 +2207,7 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>97.29025</v>
+        <v>97.22945</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.4">
@@ -2221,7 +2221,7 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>97.349900000000005</v>
+        <v>97.288889999999995</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.4">
@@ -2235,7 +2235,7 @@
         <v>0</v>
       </c>
       <c r="D88">
-        <v>97.409729999999996</v>
+        <v>97.348529999999997</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.4">
@@ -2249,7 +2249,7 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>97.469660000000005</v>
+        <v>97.408280000000005</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.4">
@@ -2263,7 +2263,7 @@
         <v>0</v>
       </c>
       <c r="D90">
-        <v>97.529619999999994</v>
+        <v>97.468059999999994</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.4">
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>97.589560000000006</v>
+        <v>97.527829999999994</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.4">
@@ -2291,7 +2291,7 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>97.649420000000006</v>
+        <v>97.587530000000001</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.4">
@@ -2305,7 +2305,7 @@
         <v>0</v>
       </c>
       <c r="D93">
-        <v>97.70917</v>
+        <v>97.647120000000001</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.4">
@@ -2319,7 +2319,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>97.768780000000007</v>
+        <v>97.706559999999996</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.4">
@@ -2333,7 +2333,7 @@
         <v>0</v>
       </c>
       <c r="D95">
-        <v>97.828209999999999</v>
+        <v>97.765839999999997</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.4">
@@ -2347,7 +2347,7 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>97.887450000000001</v>
+        <v>97.824929999999995</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.4">
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="D97">
-        <v>97.9465</v>
+        <v>97.883830000000003</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.4">
@@ -2375,7 +2375,7 @@
         <v>0</v>
       </c>
       <c r="D98">
-        <v>98.005340000000004</v>
+        <v>97.942530000000005</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.4">
@@ -2389,7 +2389,7 @@
         <v>0</v>
       </c>
       <c r="D99">
-        <v>98.063990000000004</v>
+        <v>98.00103</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.4">
@@ -2403,7 +2403,7 @@
         <v>0</v>
       </c>
       <c r="D100">
-        <v>98.122450000000001</v>
+        <v>98.059349999999995</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.4">
@@ -2417,7 +2417,7 @@
         <v>0</v>
       </c>
       <c r="D101">
-        <v>98.180729999999997</v>
+        <v>98.117490000000004</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.4">
@@ -2431,7 +2431,7 @@
         <v>0</v>
       </c>
       <c r="D102">
-        <v>98.238870000000006</v>
+        <v>98.175489999999996</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.4">
@@ -2445,7 +2445,7 @@
         <v>0</v>
       </c>
       <c r="D103">
-        <v>98.296880000000002</v>
+        <v>98.233369999999994</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.4">
@@ -2459,7 +2459,7 @@
         <v>0</v>
       </c>
       <c r="D104">
-        <v>98.354789999999994</v>
+        <v>98.291160000000005</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.4">
@@ -2473,7 +2473,7 @@
         <v>0</v>
       </c>
       <c r="D105">
-        <v>98.412639999999996</v>
+        <v>98.348879999999994</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.4">
@@ -2487,7 +2487,7 @@
         <v>0</v>
       </c>
       <c r="D106">
-        <v>98.470460000000003</v>
+        <v>98.406570000000002</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.4">
@@ -2501,7 +2501,7 @@
         <v>0</v>
       </c>
       <c r="D107">
-        <v>98.528260000000003</v>
+        <v>98.464250000000007</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.4">
@@ -2515,7 +2515,7 @@
         <v>0</v>
       </c>
       <c r="D108">
-        <v>98.586070000000007</v>
+        <v>98.521940000000001</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.4">
@@ -2529,7 +2529,7 @@
         <v>0</v>
       </c>
       <c r="D109">
-        <v>98.643910000000005</v>
+        <v>98.579650000000001</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.4">
@@ -2543,7 +2543,7 @@
         <v>0</v>
       </c>
       <c r="D110">
-        <v>98.701809999999995</v>
+        <v>98.637420000000006</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.4">
@@ -2557,7 +2557,7 @@
         <v>0</v>
       </c>
       <c r="D111">
-        <v>98.759780000000006</v>
+        <v>98.695269999999994</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.4">
@@ -2571,7 +2571,7 @@
         <v>0</v>
       </c>
       <c r="D112">
-        <v>98.817850000000007</v>
+        <v>98.753219999999999</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.4">
@@ -2585,7 +2585,7 @@
         <v>0</v>
       </c>
       <c r="D113">
-        <v>98.876040000000003</v>
+        <v>98.811279999999996</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.4">
@@ -2599,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="D114">
-        <v>98.934359999999998</v>
+        <v>98.869489999999999</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.4">
@@ -2613,7 +2613,7 @@
         <v>0</v>
       </c>
       <c r="D115">
-        <v>98.992850000000004</v>
+        <v>98.927850000000007</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.4">
@@ -2627,7 +2627,7 @@
         <v>0</v>
       </c>
       <c r="D116">
-        <v>99.051519999999996</v>
+        <v>98.986379999999997</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.4">
@@ -2641,7 +2641,7 @@
         <v>0</v>
       </c>
       <c r="D117">
-        <v>99.110389999999995</v>
+        <v>99.045109999999994</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.4">
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="D118">
-        <v>99.169460000000001</v>
+        <v>99.104050000000001</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.4">
@@ -2669,7 +2669,7 @@
         <v>0</v>
       </c>
       <c r="D119">
-        <v>99.228750000000005</v>
+        <v>99.163200000000003</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.4">
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="D120">
-        <v>99.288259999999994</v>
+        <v>99.222570000000005</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.4">
@@ -2697,7 +2697,7 @@
         <v>3</v>
       </c>
       <c r="D121">
-        <v>99.344110000000001</v>
+        <v>99.278329999999997</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.4">
@@ -2711,7 +2711,7 @@
         <v>3</v>
       </c>
       <c r="D122">
-        <v>99.391800000000003</v>
+        <v>99.326049999999995</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.4">
@@ -2725,7 +2725,7 @@
         <v>3</v>
       </c>
       <c r="D123">
-        <v>99.430480000000003</v>
+        <v>99.364900000000006</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.4">
@@ -2739,7 +2739,7 @@
         <v>3</v>
       </c>
       <c r="D124">
-        <v>99.459509999999995</v>
+        <v>99.394229999999993</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.4">
@@ -2753,7 +2753,7 @@
         <v>3</v>
       </c>
       <c r="D125">
-        <v>99.47833</v>
+        <v>99.413460000000001</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.4">
@@ -2767,7 +2767,7 @@
         <v>3</v>
       </c>
       <c r="D126">
-        <v>99.486400000000003</v>
+        <v>99.422020000000003</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.4">
@@ -2781,7 +2781,7 @@
         <v>3</v>
       </c>
       <c r="D127">
-        <v>99.483189999999993</v>
+        <v>99.419399999999996</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.4">
@@ -2795,7 +2795,7 @@
         <v>3</v>
       </c>
       <c r="D128">
-        <v>99.468249999999998</v>
+        <v>99.40513</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.4">
@@ -2809,7 +2809,7 @@
         <v>3</v>
       </c>
       <c r="D129">
-        <v>99.441220000000001</v>
+        <v>99.378820000000005</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.4">
@@ -2823,7 +2823,7 @@
         <v>3</v>
       </c>
       <c r="D130">
-        <v>99.401830000000004</v>
+        <v>99.340199999999996</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.4">
@@ -2837,7 +2837,7 @@
         <v>3</v>
       </c>
       <c r="D131">
-        <v>99.349950000000007</v>
+        <v>99.289140000000003</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.4">
@@ -2851,7 +2851,7 @@
         <v>3</v>
       </c>
       <c r="D132">
-        <v>99.285560000000004</v>
+        <v>99.225589999999997</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.4">
@@ -2865,7 +2865,7 @@
         <v>3</v>
       </c>
       <c r="D133">
-        <v>99.20872</v>
+        <v>99.149619999999999</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.4">
@@ -2879,7 +2879,7 @@
         <v>3</v>
       </c>
       <c r="D134">
-        <v>99.119619999999998</v>
+        <v>99.061409999999995</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.4">
@@ -2893,7 +2893,7 @@
         <v>3</v>
       </c>
       <c r="D135">
-        <v>99.018519999999995</v>
+        <v>98.961219999999997</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.4">
@@ -2907,7 +2907,7 @@
         <v>3</v>
       </c>
       <c r="D136">
-        <v>98.905779999999993</v>
+        <v>98.849400000000003</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.4">
@@ -2921,7 +2921,7 @@
         <v>3</v>
       </c>
       <c r="D137">
-        <v>98.781779999999998</v>
+        <v>98.726330000000004</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.4">
@@ -2935,7 +2935,7 @@
         <v>0</v>
       </c>
       <c r="D138">
-        <v>98.650139999999993</v>
+        <v>98.595579999999998</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.4">
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="D139">
-        <v>98.515060000000005</v>
+        <v>98.461280000000002</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.4">
@@ -2963,7 +2963,7 @@
         <v>0</v>
       </c>
       <c r="D140">
-        <v>98.377960000000002</v>
+        <v>98.324860000000001</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.4">
@@ -2977,7 +2977,7 @@
         <v>0</v>
       </c>
       <c r="D141">
-        <v>98.24015</v>
+        <v>98.187600000000003</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.4">
@@ -2991,7 +2991,7 @@
         <v>0</v>
       </c>
       <c r="D142">
-        <v>98.102879999999999</v>
+        <v>98.05077</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.4">
@@ -3005,7 +3005,7 @@
         <v>0</v>
       </c>
       <c r="D143">
-        <v>97.967389999999995</v>
+        <v>97.915610000000001</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.4">
@@ -3019,7 +3019,7 @@
         <v>0</v>
       </c>
       <c r="D144">
-        <v>97.83484</v>
+        <v>97.78331</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.4">
@@ -3033,7 +3033,7 @@
         <v>0</v>
       </c>
       <c r="D145">
-        <v>97.706360000000004</v>
+        <v>97.654989999999998</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.4">
@@ -3047,7 +3047,7 @@
         <v>0</v>
       </c>
       <c r="D146">
-        <v>97.582930000000005</v>
+        <v>97.531639999999996</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.4">
@@ -3061,7 +3061,7 @@
         <v>0</v>
       </c>
       <c r="D147">
-        <v>97.465400000000002</v>
+        <v>97.41413</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.4">
@@ -3075,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="D148">
-        <v>97.354470000000006</v>
+        <v>97.303160000000005</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.4">
@@ -3089,7 +3089,7 @@
         <v>0</v>
       </c>
       <c r="D149">
-        <v>97.250699999999995</v>
+        <v>97.199290000000005</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.4">
@@ -3103,7 +3103,7 @@
         <v>0</v>
       </c>
       <c r="D150">
-        <v>97.154499999999999</v>
+        <v>97.102940000000004</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.4">
@@ -3117,7 +3117,7 @@
         <v>0</v>
       </c>
       <c r="D151">
-        <v>97.066130000000001</v>
+        <v>97.014380000000003</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.4">
@@ -3131,7 +3131,7 @@
         <v>0</v>
       </c>
       <c r="D152">
-        <v>96.985749999999996</v>
+        <v>96.933790000000002</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.4">
@@ -3145,7 +3145,7 @@
         <v>0</v>
       </c>
       <c r="D153">
-        <v>96.913420000000002</v>
+        <v>96.86121</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.4">
@@ -3159,7 +3159,7 @@
         <v>0</v>
       </c>
       <c r="D154">
-        <v>96.849090000000004</v>
+        <v>96.796629999999993</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.4">
@@ -3173,7 +3173,7 @@
         <v>0</v>
       </c>
       <c r="D155">
-        <v>96.792680000000004</v>
+        <v>96.739940000000004</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.4">
@@ -3187,7 +3187,7 @@
         <v>0</v>
       </c>
       <c r="D156">
-        <v>96.744020000000006</v>
+        <v>96.690989999999999</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.4">
@@ -3201,7 +3201,7 @@
         <v>0</v>
       </c>
       <c r="D157">
-        <v>96.702920000000006</v>
+        <v>96.64958</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.4">
@@ -3215,7 +3215,7 @@
         <v>0</v>
       </c>
       <c r="D158">
-        <v>96.669160000000005</v>
+        <v>96.615480000000005</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.4">
@@ -3229,7 +3229,7 @@
         <v>0</v>
       </c>
       <c r="D159">
-        <v>96.642489999999995</v>
+        <v>96.588459999999998</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.4">
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="D160">
-        <v>96.622630000000001</v>
+        <v>96.568240000000003</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.4">
@@ -3257,7 +3257,7 @@
         <v>0</v>
       </c>
       <c r="D161">
-        <v>96.609290000000001</v>
+        <v>96.55453</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.4">
@@ -3271,7 +3271,7 @@
         <v>0</v>
       </c>
       <c r="D162">
-        <v>96.602159999999998</v>
+        <v>96.547039999999996</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.4">
@@ -3285,7 +3285,7 @@
         <v>0</v>
       </c>
       <c r="D163">
-        <v>96.600939999999994</v>
+        <v>96.545460000000006</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.4">
@@ -3299,7 +3299,7 @@
         <v>0</v>
       </c>
       <c r="D164">
-        <v>96.6053</v>
+        <v>96.549469999999999</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.4">
@@ -3313,7 +3313,7 @@
         <v>0</v>
       </c>
       <c r="D165">
-        <v>96.614930000000001</v>
+        <v>96.558760000000007</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.4">
@@ -3327,7 +3327,7 @@
         <v>0</v>
       </c>
       <c r="D166">
-        <v>96.629509999999996</v>
+        <v>96.572999999999993</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.4">
@@ -3341,7 +3341,7 @@
         <v>0</v>
       </c>
       <c r="D167">
-        <v>96.64873</v>
+        <v>96.59187</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.4">
@@ -3355,7 +3355,7 @@
         <v>0</v>
       </c>
       <c r="D168">
-        <v>96.672269999999997</v>
+        <v>96.615080000000006</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.4">
@@ -3369,7 +3369,7 @@
         <v>0</v>
       </c>
       <c r="D169">
-        <v>96.699809999999999</v>
+        <v>96.642309999999995</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.4">
@@ -3383,7 +3383,7 @@
         <v>0</v>
       </c>
       <c r="D170">
-        <v>96.731049999999996</v>
+        <v>96.673270000000002</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.4">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="D171">
-        <v>96.765709999999999</v>
+        <v>96.707669999999993</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.4">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="D172">
-        <v>96.8035</v>
+        <v>96.74521</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.4">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="D173">
-        <v>96.844170000000005</v>
+        <v>96.785640000000001</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.4">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="D174">
-        <v>96.887460000000004</v>
+        <v>96.828680000000006</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.4">
@@ -3453,7 +3453,7 @@
         <v>0</v>
       </c>
       <c r="D175">
-        <v>96.933099999999996</v>
+        <v>96.874070000000003</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.4">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="D176">
-        <v>96.980869999999996</v>
+        <v>96.921570000000003</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.4">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="D177">
-        <v>97.030510000000007</v>
+        <v>96.970960000000005</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.4">
@@ -3495,7 +3495,7 @@
         <v>0</v>
       </c>
       <c r="D178">
-        <v>97.081789999999998</v>
+        <v>97.022019999999998</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.4">
@@ -3509,7 +3509,7 @@
         <v>0</v>
       </c>
       <c r="D179">
-        <v>97.134540000000001</v>
+        <v>97.074550000000002</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.4">
@@ -3523,7 +3523,7 @@
         <v>0</v>
       </c>
       <c r="D180">
-        <v>97.188540000000003</v>
+        <v>97.128360000000001</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.4">
@@ -3537,7 +3537,7 @@
         <v>0</v>
       </c>
       <c r="D181">
-        <v>97.243629999999996</v>
+        <v>97.183260000000004</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.4">
@@ -3551,7 +3551,7 @@
         <v>0</v>
       </c>
       <c r="D182">
-        <v>97.299639999999997</v>
+        <v>97.239080000000001</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.4">
@@ -3565,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="D183">
-        <v>97.35642</v>
+        <v>97.295659999999998</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.4">
@@ -3579,7 +3579,7 @@
         <v>0</v>
       </c>
       <c r="D184">
-        <v>97.413820000000001</v>
+        <v>97.352869999999996</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.4">
@@ -3593,7 +3593,7 @@
         <v>0</v>
       </c>
       <c r="D185">
-        <v>97.471720000000005</v>
+        <v>97.410570000000007</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.4">
@@ -3607,7 +3607,7 @@
         <v>0</v>
       </c>
       <c r="D186">
-        <v>97.529989999999998</v>
+        <v>97.468639999999994</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.4">
@@ -3621,7 +3621,7 @@
         <v>0</v>
       </c>
       <c r="D187">
-        <v>97.588520000000003</v>
+        <v>97.526989999999998</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.4">
@@ -3635,7 +3635,7 @@
         <v>0</v>
       </c>
       <c r="D188">
-        <v>97.647239999999996</v>
+        <v>97.585509999999999</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.4">
@@ -3649,7 +3649,7 @@
         <v>0</v>
       </c>
       <c r="D189">
-        <v>97.706040000000002</v>
+        <v>97.644139999999993</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.4">
@@ -3663,7 +3663,7 @@
         <v>0</v>
       </c>
       <c r="D190">
-        <v>97.764870000000002</v>
+        <v>97.702799999999996</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.4">
@@ -3677,7 +3677,7 @@
         <v>0</v>
       </c>
       <c r="D191">
-        <v>97.823660000000004</v>
+        <v>97.761430000000004</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.4">
@@ -3691,7 +3691,7 @@
         <v>0</v>
       </c>
       <c r="D192">
-        <v>97.882379999999998</v>
+        <v>97.819990000000004</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.4">
@@ -3705,7 +3705,7 @@
         <v>0</v>
       </c>
       <c r="D193">
-        <v>97.940979999999996</v>
+        <v>97.878439999999998</v>
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.4">
@@ -3719,7 +3719,7 @@
         <v>0</v>
       </c>
       <c r="D194">
-        <v>97.999440000000007</v>
+        <v>97.93674</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.4">
@@ -3733,7 +3733,7 @@
         <v>0</v>
       </c>
       <c r="D195">
-        <v>98.05771</v>
+        <v>97.994879999999995</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.4">
@@ -3747,7 +3747,7 @@
         <v>0</v>
       </c>
       <c r="D196">
-        <v>98.115799999999993</v>
+        <v>98.052819999999997</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.4">
@@ -3761,7 +3761,7 @@
         <v>0</v>
       </c>
       <c r="D197">
-        <v>98.173699999999997</v>
+        <v>98.110569999999996</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.4">
@@ -3775,7 +3775,7 @@
         <v>0</v>
       </c>
       <c r="D198">
-        <v>98.231390000000005</v>
+        <v>98.168120000000002</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.4">
@@ -3789,7 +3789,7 @@
         <v>0</v>
       </c>
       <c r="D199">
-        <v>98.288880000000006</v>
+        <v>98.225470000000001</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.4">
@@ -3803,7 +3803,7 @@
         <v>0</v>
       </c>
       <c r="D200">
-        <v>98.346190000000007</v>
+        <v>98.282640000000001</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.4">
@@ -3817,7 +3817,7 @@
         <v>0</v>
       </c>
       <c r="D201">
-        <v>98.403319999999994</v>
+        <v>98.339650000000006</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.4">
@@ -3831,7 +3831,7 @@
         <v>0</v>
       </c>
       <c r="D202">
-        <v>98.460310000000007</v>
+        <v>98.396500000000003</v>
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.4">
@@ -3845,7 +3845,7 @@
         <v>0</v>
       </c>
       <c r="D203">
-        <v>98.517169999999993</v>
+        <v>98.453239999999994</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.4">
@@ -3859,7 +3859,7 @@
         <v>0</v>
       </c>
       <c r="D204">
-        <v>98.573939999999993</v>
+        <v>98.509879999999995</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.4">
@@ -3873,7 +3873,7 @@
         <v>0</v>
       </c>
       <c r="D205">
-        <v>98.630650000000003</v>
+        <v>98.566469999999995</v>
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.4">
@@ -3887,7 +3887,7 @@
         <v>0</v>
       </c>
       <c r="D206">
-        <v>98.68732</v>
+        <v>98.623019999999997</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.4">
@@ -3901,7 +3901,7 @@
         <v>0</v>
       </c>
       <c r="D207">
-        <v>98.743989999999997</v>
+        <v>98.679569999999998</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.4">
@@ -3915,7 +3915,7 @@
         <v>0</v>
       </c>
       <c r="D208">
-        <v>98.800669999999997</v>
+        <v>98.736130000000003</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.4">
@@ -3929,7 +3929,7 @@
         <v>0</v>
       </c>
       <c r="D209">
-        <v>98.857389999999995</v>
+        <v>98.792730000000006</v>
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.4">
@@ -3943,7 +3943,7 @@
         <v>0</v>
       </c>
       <c r="D210">
-        <v>98.914159999999995</v>
+        <v>98.849379999999996</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.4">
@@ -3957,7 +3957,7 @@
         <v>0</v>
       </c>
       <c r="D211">
-        <v>98.971010000000007</v>
+        <v>98.906109999999998</v>
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.4">
@@ -3971,7 +3971,7 @@
         <v>0</v>
       </c>
       <c r="D212">
-        <v>99.027959999999993</v>
+        <v>98.962940000000003</v>
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.4">
@@ -3985,7 +3985,7 @@
         <v>0</v>
       </c>
       <c r="D213">
-        <v>99.085040000000006</v>
+        <v>99.019900000000007</v>
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.4">
@@ -3999,7 +3999,7 @@
         <v>0</v>
       </c>
       <c r="D214">
-        <v>99.142259999999993</v>
+        <v>99.076999999999998</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.4">
@@ -4013,7 +4013,7 @@
         <v>0</v>
       </c>
       <c r="D215">
-        <v>99.199650000000005</v>
+        <v>99.134270000000001</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.4">
@@ -4027,7 +4027,7 @@
         <v>0</v>
       </c>
       <c r="D216">
-        <v>99.257220000000004</v>
+        <v>99.19171</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.4">
@@ -4041,7 +4041,7 @@
         <v>0</v>
       </c>
       <c r="D217">
-        <v>99.314989999999995</v>
+        <v>99.249350000000007</v>
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.4">
@@ -4055,7 +4055,7 @@
         <v>0</v>
       </c>
       <c r="D218">
-        <v>99.372979999999998</v>
+        <v>99.307199999999995</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.4">
@@ -4069,7 +4069,7 @@
         <v>0</v>
       </c>
       <c r="D219">
-        <v>99.431190000000001</v>
+        <v>99.365269999999995</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.4">
@@ -4083,7 +4083,7 @@
         <v>0</v>
       </c>
       <c r="D220">
-        <v>99.489620000000002</v>
+        <v>99.423569999999998</v>
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.4">
@@ -4097,7 +4097,7 @@
         <v>3</v>
       </c>
       <c r="D221">
-        <v>99.544390000000007</v>
+        <v>99.478260000000006</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.4">
@@ -4111,7 +4111,7 @@
         <v>3</v>
       </c>
       <c r="D222">
-        <v>99.590999999999994</v>
+        <v>99.524900000000002</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.4">
@@ -4125,7 +4125,7 @@
         <v>3</v>
       </c>
       <c r="D223">
-        <v>99.628600000000006</v>
+        <v>99.562669999999997</v>
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.4">
@@ -4139,7 +4139,7 @@
         <v>3</v>
       </c>
       <c r="D224">
-        <v>99.656540000000007</v>
+        <v>99.590909999999994</v>
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.4">
@@ -4153,7 +4153,7 @@
         <v>3</v>
       </c>
       <c r="D225">
-        <v>99.674279999999996</v>
+        <v>99.609059999999999</v>
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.4">
@@ -4167,7 +4167,7 @@
         <v>3</v>
       </c>
       <c r="D226">
-        <v>99.681250000000006</v>
+        <v>99.616529999999997</v>
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.4">
@@ -4181,7 +4181,7 @@
         <v>3</v>
       </c>
       <c r="D227">
-        <v>99.676940000000002</v>
+        <v>99.612819999999999</v>
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.4">
@@ -4195,7 +4195,7 @@
         <v>3</v>
       </c>
       <c r="D228">
-        <v>99.660910000000001</v>
+        <v>99.597449999999995</v>
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.4">
@@ -4209,7 +4209,7 @@
         <v>3</v>
       </c>
       <c r="D229">
-        <v>99.632769999999994</v>
+        <v>99.570040000000006</v>
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.4">
@@ -4223,7 +4223,7 @@
         <v>3</v>
       </c>
       <c r="D230">
-        <v>99.592280000000002</v>
+        <v>99.530330000000006</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.4">
@@ -4237,7 +4237,7 @@
         <v>3</v>
       </c>
       <c r="D231">
-        <v>99.539320000000004</v>
+        <v>99.478179999999995</v>
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.4">
@@ -4251,7 +4251,7 @@
         <v>3</v>
       </c>
       <c r="D232">
-        <v>99.473830000000007</v>
+        <v>99.413539999999998</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.4">
@@ -4265,7 +4265,7 @@
         <v>3</v>
       </c>
       <c r="D233">
-        <v>99.395899999999997</v>
+        <v>99.336479999999995</v>
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.4">
@@ -4279,7 +4279,7 @@
         <v>3</v>
       </c>
       <c r="D234">
-        <v>99.305710000000005</v>
+        <v>99.247190000000003</v>
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.4">
@@ -4293,7 +4293,7 @@
         <v>3</v>
       </c>
       <c r="D235">
-        <v>99.203540000000004</v>
+        <v>99.145930000000007</v>
       </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.4">
@@ -4307,7 +4307,7 @@
         <v>3</v>
       </c>
       <c r="D236">
-        <v>99.08972</v>
+        <v>99.03304</v>
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.4">
@@ -4321,7 +4321,7 @@
         <v>3</v>
       </c>
       <c r="D237">
-        <v>98.964650000000006</v>
+        <v>98.908900000000003</v>
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.4">
@@ -4335,7 +4335,7 @@
         <v>0</v>
       </c>
       <c r="D238">
-        <v>98.831959999999995</v>
+        <v>98.777100000000004</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.4">
@@ -4349,7 +4349,7 @@
         <v>0</v>
       </c>
       <c r="D239">
-        <v>98.695840000000004</v>
+        <v>98.641769999999994</v>
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.4">
@@ -4363,7 +4363,7 @@
         <v>0</v>
       </c>
       <c r="D240">
-        <v>98.557720000000003</v>
+        <v>98.504320000000007</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.4">
@@ -4377,7 +4377,7 @@
         <v>0</v>
       </c>
       <c r="D241">
-        <v>98.418899999999994</v>
+        <v>98.366060000000004</v>
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.4">
@@ -4391,7 +4391,7 @@
         <v>0</v>
       </c>
       <c r="D242">
-        <v>98.280649999999994</v>
+        <v>98.22824</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.4">
@@ -4405,7 +4405,7 @@
         <v>0</v>
       </c>
       <c r="D243">
-        <v>98.144180000000006</v>
+        <v>98.092119999999994</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.4">
@@ -4419,7 +4419,7 @@
         <v>0</v>
       </c>
       <c r="D244">
-        <v>98.010689999999997</v>
+        <v>97.958870000000005</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.4">
@@ -4433,7 +4433,7 @@
         <v>0</v>
       </c>
       <c r="D245">
-        <v>97.881270000000001</v>
+        <v>97.829620000000006</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.4">
@@ -4447,7 +4447,7 @@
         <v>0</v>
       </c>
       <c r="D246">
-        <v>97.756919999999994</v>
+        <v>97.705349999999996</v>
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.4">
@@ -4461,7 +4461,7 @@
         <v>0</v>
       </c>
       <c r="D247">
-        <v>97.638490000000004</v>
+        <v>97.586939999999998</v>
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.4">
@@ -4475,7 +4475,7 @@
         <v>0</v>
       </c>
       <c r="D248">
-        <v>97.526669999999996</v>
+        <v>97.475080000000005</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.4">
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="D249">
-        <v>97.422030000000007</v>
+        <v>97.370339999999999</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.4">
@@ -4503,7 +4503,7 @@
         <v>0</v>
       </c>
       <c r="D250">
-        <v>97.324960000000004</v>
+        <v>97.273129999999995</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.4">
@@ -4517,7 +4517,7 @@
         <v>0</v>
       </c>
       <c r="D251">
-        <v>97.235740000000007</v>
+        <v>97.183719999999994</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.4">
@@ -4531,7 +4531,7 @@
         <v>0</v>
       </c>
       <c r="D252">
-        <v>97.154529999999994</v>
+        <v>97.102279999999993</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.4">
@@ -4545,7 +4545,7 @@
         <v>0</v>
       </c>
       <c r="D253">
-        <v>97.081360000000004</v>
+        <v>97.028880000000001</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.4">
@@ -4559,7 +4559,7 @@
         <v>0</v>
       </c>
       <c r="D254">
-        <v>97.016210000000001</v>
+        <v>96.963480000000004</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.4">
@@ -4573,7 +4573,7 @@
         <v>0</v>
       </c>
       <c r="D255">
-        <v>96.958979999999997</v>
+        <v>96.90598</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.4">
@@ -4587,7 +4587,7 @@
         <v>0</v>
       </c>
       <c r="D256">
-        <v>96.909520000000001</v>
+        <v>96.856219999999993</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.4">
@@ -4601,7 +4601,7 @@
         <v>0</v>
       </c>
       <c r="D257">
-        <v>96.867620000000002</v>
+        <v>96.813999999999993</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.4">
@@ -4615,7 +4615,7 @@
         <v>0</v>
       </c>
       <c r="D258">
-        <v>96.833070000000006</v>
+        <v>96.779120000000006</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.4">
@@ -4629,7 +4629,7 @@
         <v>0</v>
       </c>
       <c r="D259">
-        <v>96.805599999999998</v>
+        <v>96.751300000000001</v>
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.4">
@@ -4643,7 +4643,7 @@
         <v>0</v>
       </c>
       <c r="D260">
-        <v>96.784959999999998</v>
+        <v>96.7303</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.4">
@@ -4657,7 +4657,7 @@
         <v>0</v>
       </c>
       <c r="D261">
-        <v>96.770830000000004</v>
+        <v>96.715810000000005</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.4">
@@ -4671,7 +4671,7 @@
         <v>0</v>
       </c>
       <c r="D262">
-        <v>96.762929999999997</v>
+        <v>96.707539999999995</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.4">
@@ -4685,7 +4685,7 @@
         <v>0</v>
       </c>
       <c r="D263">
-        <v>96.760930000000002</v>
+        <v>96.705190000000002</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.4">
@@ -4699,7 +4699,7 @@
         <v>0</v>
       </c>
       <c r="D264">
-        <v>96.764520000000005</v>
+        <v>96.708430000000007</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.4">
@@ -4713,7 +4713,7 @@
         <v>0</v>
       </c>
       <c r="D265">
-        <v>96.773380000000003</v>
+        <v>96.716949999999997</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.4">
@@ -4727,7 +4727,7 @@
         <v>0</v>
       </c>
       <c r="D266">
-        <v>96.787199999999999</v>
+        <v>96.730419999999995</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.4">
@@ -4741,7 +4741,7 @@
         <v>0</v>
       </c>
       <c r="D267">
-        <v>96.80565</v>
+        <v>96.748540000000006</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.4">
@@ -4755,7 +4755,7 @@
         <v>0</v>
       </c>
       <c r="D268">
-        <v>96.828429999999997</v>
+        <v>96.770979999999994</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.4">
@@ -4769,7 +4769,7 @@
         <v>0</v>
       </c>
       <c r="D269">
-        <v>96.85521</v>
+        <v>96.797449999999998</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.4">
@@ -4783,7 +4783,7 @@
         <v>0</v>
       </c>
       <c r="D270">
-        <v>96.885689999999997</v>
+        <v>96.827659999999995</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.4">
@@ -4797,7 +4797,7 @@
         <v>0</v>
       </c>
       <c r="D271">
-        <v>96.919589999999999</v>
+        <v>96.8613</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.4">
@@ -4811,7 +4811,7 @@
         <v>0</v>
       </c>
       <c r="D272">
-        <v>96.956630000000004</v>
+        <v>96.898089999999996</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.4">
@@ -4825,7 +4825,7 @@
         <v>0</v>
       </c>
       <c r="D273">
-        <v>96.996539999999996</v>
+        <v>96.93777</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.4">
@@ -4839,7 +4839,7 @@
         <v>0</v>
       </c>
       <c r="D274">
-        <v>97.039079999999998</v>
+        <v>96.980059999999995</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.4">
@@ -4853,7 +4853,7 @@
         <v>0</v>
       </c>
       <c r="D275">
-        <v>97.083969999999994</v>
+        <v>97.024699999999996</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.4">
@@ -4867,7 +4867,7 @@
         <v>0</v>
       </c>
       <c r="D276">
-        <v>97.130989999999997</v>
+        <v>97.071449999999999</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.4">
@@ -4881,7 +4881,7 @@
         <v>0</v>
       </c>
       <c r="D277">
-        <v>97.179879999999997</v>
+        <v>97.120090000000005</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.4">
@@ -4895,7 +4895,7 @@
         <v>0</v>
       </c>
       <c r="D278">
-        <v>97.230419999999995</v>
+        <v>97.170410000000004</v>
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.4">
@@ -4909,7 +4909,7 @@
         <v>0</v>
       </c>
       <c r="D279">
-        <v>97.282420000000002</v>
+        <v>97.222200000000001</v>
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.4">
@@ -4923,7 +4923,7 @@
         <v>0</v>
       </c>
       <c r="D280">
-        <v>97.335679999999996</v>
+        <v>97.275260000000003</v>
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.4">
@@ -4937,7 +4937,7 @@
         <v>0</v>
       </c>
       <c r="D281">
-        <v>97.390029999999996</v>
+        <v>97.329419999999999</v>
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.4">
@@ -4951,7 +4951,7 @@
         <v>0</v>
       </c>
       <c r="D282">
-        <v>97.445300000000003</v>
+        <v>97.384510000000006</v>
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.4">
@@ -4965,7 +4965,7 @@
         <v>0</v>
       </c>
       <c r="D283">
-        <v>97.501350000000002</v>
+        <v>97.440349999999995</v>
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.4">
@@ -4979,7 +4979,7 @@
         <v>0</v>
       </c>
       <c r="D284">
-        <v>97.558009999999996</v>
+        <v>97.496830000000003</v>
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.4">
@@ -4993,7 +4993,7 @@
         <v>0</v>
       </c>
       <c r="D285">
-        <v>97.615179999999995</v>
+        <v>97.553799999999995</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.4">
@@ -5007,7 +5007,7 @@
         <v>0</v>
       </c>
       <c r="D286">
-        <v>97.672719999999998</v>
+        <v>97.611140000000006</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.4">
@@ -5021,7 +5021,7 @@
         <v>0</v>
       </c>
       <c r="D287">
-        <v>97.730530000000002</v>
+        <v>97.668760000000006</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.4">
@@ -5035,7 +5035,7 @@
         <v>0</v>
       </c>
       <c r="D288">
-        <v>97.788520000000005</v>
+        <v>97.726560000000006</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.4">
@@ -5049,7 +5049,7 @@
         <v>0</v>
       </c>
       <c r="D289">
-        <v>97.846590000000006</v>
+        <v>97.784469999999999</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.4">
@@ -5063,7 +5063,7 @@
         <v>0</v>
       </c>
       <c r="D290">
-        <v>97.904700000000005</v>
+        <v>97.842410000000001</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.4">
@@ -5077,7 +5077,7 @@
         <v>0</v>
       </c>
       <c r="D291">
-        <v>97.962779999999995</v>
+        <v>97.900319999999994</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.4">
@@ -5091,7 +5091,7 @@
         <v>0</v>
       </c>
       <c r="D292">
-        <v>98.020780000000002</v>
+        <v>97.958169999999996</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.4">
@@ -5105,7 +5105,7 @@
         <v>0</v>
       </c>
       <c r="D293">
-        <v>98.078670000000002</v>
+        <v>98.015900000000002</v>
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.4">
@@ -5119,7 +5119,7 @@
         <v>0</v>
       </c>
       <c r="D294">
-        <v>98.136409999999998</v>
+        <v>98.073499999999996</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.4">
@@ -5133,7 +5133,7 @@
         <v>0</v>
       </c>
       <c r="D295">
-        <v>98.193979999999996</v>
+        <v>98.130920000000003</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.4">
@@ -5147,7 +5147,7 @@
         <v>0</v>
       </c>
       <c r="D296">
-        <v>98.251360000000005</v>
+        <v>98.188159999999996</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.4">
@@ -5161,7 +5161,7 @@
         <v>0</v>
       </c>
       <c r="D297">
-        <v>98.308549999999997</v>
+        <v>98.24521</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.4">
@@ -5175,7 +5175,7 @@
         <v>0</v>
       </c>
       <c r="D298">
-        <v>98.365539999999996</v>
+        <v>98.302059999999997</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.4">
@@ -5189,7 +5189,7 @@
         <v>0</v>
       </c>
       <c r="D299">
-        <v>98.422340000000005</v>
+        <v>98.358720000000005</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.4">
@@ -5203,7 +5203,7 @@
         <v>0</v>
       </c>
       <c r="D300">
-        <v>98.478949999999998</v>
+        <v>98.415189999999996</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.4">
@@ -5217,7 +5217,7 @@
         <v>0</v>
       </c>
       <c r="D301">
-        <v>98.535390000000007</v>
+        <v>98.471500000000006</v>
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.4">
@@ -5231,7 +5231,7 @@
         <v>0</v>
       </c>
       <c r="D302">
-        <v>98.591679999999997</v>
+        <v>98.527670000000001</v>
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.4">
@@ -5245,7 +5245,7 @@
         <v>0</v>
       </c>
       <c r="D303">
-        <v>98.647859999999994</v>
+        <v>98.58372</v>
       </c>
     </row>
   </sheetData>

--- a/inputs/data_symbols_TD/11_LTAN06_800km_1213COLD_MY_ALL_HEAT_MY_Black.xlsx
+++ b/inputs/data_symbols_TD/11_LTAN06_800km_1213COLD_MY_ALL_HEAT_MY_Black.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\inputs\data_symbols_TD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ED96E69D-DCA6-404F-9952-9A7FB06EECD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{934C5B46-0893-49BE-B502-0EBF0AA0CBEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="18900" windowHeight="10965" xr2:uid="{AD03C37C-919F-4AF3-BE2B-FE497CDDD6D2}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{B51CEB01-67F3-4AD7-ADC5-C172FD9B892E}"/>
   </bookViews>
   <sheets>
     <sheet name="11_LTAN06_800km_1213COLD_MY_ALL" sheetId="1" r:id="rId1"/>
@@ -1002,7 +1002,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E57D1B09-8D91-48D4-830C-FDFF200658F4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4225F9D4-211E-46EF-B487-34920ED09A3D}">
   <dimension ref="A1:D303"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>

--- a/inputs/data_symbols_TD/11_LTAN06_800km_1213COLD_MY_ALL_HEAT_MY_Black.xlsx
+++ b/inputs/data_symbols_TD/11_LTAN06_800km_1213COLD_MY_ALL_HEAT_MY_Black.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\inputs\data_symbols_TD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{934C5B46-0893-49BE-B502-0EBF0AA0CBEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8F3DBF6E-4406-456C-881F-D3DDF4A53BD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{B51CEB01-67F3-4AD7-ADC5-C172FD9B892E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{74233173-10D2-40C5-AC54-CF8090E8D18B}"/>
   </bookViews>
   <sheets>
     <sheet name="11_LTAN06_800km_1213COLD_MY_ALL" sheetId="1" r:id="rId1"/>
@@ -1002,7 +1002,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4225F9D4-211E-46EF-B487-34920ED09A3D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9231FC0-625A-458D-952F-3F7E63BBD333}">
   <dimension ref="A1:D303"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
